--- a/output/analysis_results.xlsx
+++ b/output/analysis_results.xlsx
@@ -1157,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1480,6 +1480,150 @@
         <v>21.2</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>All patients</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" t="n">
+        <v>63</v>
+      </c>
+      <c r="E14" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>69.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>All patients</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>24</v>
+      </c>
+      <c r="D15" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="F15" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>All patients</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>36</v>
+      </c>
+      <c r="D16" t="n">
+        <v>31</v>
+      </c>
+      <c r="E16" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="F16" t="n">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PFS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>All patients</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>12</v>
+      </c>
+      <c r="D17" t="n">
+        <v>49</v>
+      </c>
+      <c r="E17" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="F17" t="n">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PFS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>All patients</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>24</v>
+      </c>
+      <c r="D18" t="n">
+        <v>31</v>
+      </c>
+      <c r="E18" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="F18" t="n">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PFS</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>All patients</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>36</v>
+      </c>
+      <c r="D19" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
